--- a/artfynd/A 28699-2022 artfynd.xlsx
+++ b/artfynd/A 28699-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121589523</v>
+        <v>121589507</v>
       </c>
       <c r="B2" t="n">
-        <v>97059</v>
+        <v>79719</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>650311</v>
+        <v>650583</v>
       </c>
       <c r="R2" t="n">
-        <v>7165804</v>
+        <v>7165463</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,6 +755,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På sälg vid hyggeskant</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121589536</v>
+        <v>121589509</v>
       </c>
       <c r="B3" t="n">
-        <v>97059</v>
+        <v>103619</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,16 +802,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>222412</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -825,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>649974</v>
+        <v>650424</v>
       </c>
       <c r="R3" t="n">
-        <v>7165915</v>
+        <v>7165645</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121589531</v>
+        <v>121589502</v>
       </c>
       <c r="B4" t="n">
-        <v>74715</v>
+        <v>79726</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +904,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>6464</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>650071</v>
+        <v>650507</v>
       </c>
       <c r="R4" t="n">
-        <v>7165870</v>
+        <v>7165565</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -993,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121589530</v>
+        <v>121589535</v>
       </c>
       <c r="B5" t="n">
-        <v>79718</v>
+        <v>82393</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1010,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6461</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1031,16 +1036,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>650084</v>
+        <v>650021</v>
       </c>
       <c r="R5" t="n">
-        <v>7165861</v>
+        <v>7165883</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1081,6 +1089,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1099,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121589509</v>
+        <v>121589531</v>
       </c>
       <c r="B6" t="n">
-        <v>103619</v>
+        <v>74715</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1120,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222412</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1143,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650424</v>
+        <v>650071</v>
       </c>
       <c r="R6" t="n">
-        <v>7165645</v>
+        <v>7165870</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1205,10 +1214,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121589528</v>
+        <v>121589532</v>
       </c>
       <c r="B7" t="n">
-        <v>103619</v>
+        <v>74715</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1226,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222412</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1249,10 +1258,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650094</v>
+        <v>650059</v>
       </c>
       <c r="R7" t="n">
-        <v>7165838</v>
+        <v>7165875</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1417,10 +1426,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121589529</v>
+        <v>121589528</v>
       </c>
       <c r="B9" t="n">
-        <v>56560</v>
+        <v>103619</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,36 +1438,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>222412</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
@@ -1468,7 +1473,7 @@
         <v>650094</v>
       </c>
       <c r="R9" t="n">
-        <v>7165843</v>
+        <v>7165838</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1501,11 +1506,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-08-09</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Uppflog, ca 6 yngre honor</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1532,10 +1532,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121589502</v>
+        <v>121589523</v>
       </c>
       <c r="B10" t="n">
-        <v>79726</v>
+        <v>97059</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1548,21 +1548,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6464</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>650507</v>
+        <v>650311</v>
       </c>
       <c r="R10" t="n">
-        <v>7165565</v>
+        <v>7165804</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1638,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121589505</v>
+        <v>121589530</v>
       </c>
       <c r="B11" t="n">
-        <v>103619</v>
+        <v>79718</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1654,21 +1654,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222412</v>
+        <v>6461</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1682,10 +1682,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>650561</v>
+        <v>650084</v>
       </c>
       <c r="R11" t="n">
-        <v>7165488</v>
+        <v>7165861</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1744,10 +1744,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121589518</v>
+        <v>121589525</v>
       </c>
       <c r="B12" t="n">
-        <v>74715</v>
+        <v>57509</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1760,21 +1760,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1782,16 +1782,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>650366</v>
+        <v>650311</v>
       </c>
       <c r="R12" t="n">
-        <v>7165752</v>
+        <v>7165805</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1824,6 +1832,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Varnande läte</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1850,10 +1863,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121589538</v>
+        <v>121589533</v>
       </c>
       <c r="B13" t="n">
-        <v>103619</v>
+        <v>78609</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1862,25 +1875,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222412</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1894,10 +1907,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>649959</v>
+        <v>650036</v>
       </c>
       <c r="R13" t="n">
-        <v>7165924</v>
+        <v>7165894</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1956,10 +1969,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121589533</v>
+        <v>121589536</v>
       </c>
       <c r="B14" t="n">
-        <v>78609</v>
+        <v>97059</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1968,25 +1981,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2000,10 +2013,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>650036</v>
+        <v>649974</v>
       </c>
       <c r="R14" t="n">
-        <v>7165894</v>
+        <v>7165915</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2173,10 +2186,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121589516</v>
+        <v>121589522</v>
       </c>
       <c r="B16" t="n">
-        <v>97065</v>
+        <v>79719</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2189,21 +2202,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221941</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2217,10 +2230,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>650368</v>
+        <v>650331</v>
       </c>
       <c r="R16" t="n">
-        <v>7165736</v>
+        <v>7165784</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2253,6 +2266,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2279,10 +2297,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121589522</v>
+        <v>121589514</v>
       </c>
       <c r="B17" t="n">
-        <v>79719</v>
+        <v>57372</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2291,25 +2309,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2323,10 +2341,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>650331</v>
+        <v>650381</v>
       </c>
       <c r="R17" t="n">
-        <v>7165784</v>
+        <v>7165754</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2363,7 +2381,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>Födosökshack på tallhögstubbe</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2390,10 +2408,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121589514</v>
+        <v>121589529</v>
       </c>
       <c r="B18" t="n">
-        <v>57372</v>
+        <v>56560</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2406,16 +2424,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2425,19 +2443,23 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>650381</v>
+        <v>650094</v>
       </c>
       <c r="R18" t="n">
-        <v>7165754</v>
+        <v>7165843</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2474,7 +2496,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Födosökshack på tallhögstubbe</t>
+          <t>Uppflog, ca 6 yngre honor</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2501,10 +2523,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121589535</v>
+        <v>121589538</v>
       </c>
       <c r="B19" t="n">
-        <v>82393</v>
+        <v>103619</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2513,25 +2535,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>222412</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2539,19 +2561,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>650021</v>
+        <v>649959</v>
       </c>
       <c r="R19" t="n">
-        <v>7165883</v>
+        <v>7165924</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2592,7 +2611,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2611,10 +2629,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121589507</v>
+        <v>121589513</v>
       </c>
       <c r="B20" t="n">
-        <v>79719</v>
+        <v>79718</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2627,21 +2645,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>6461</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2655,10 +2673,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>650583</v>
+        <v>650383</v>
       </c>
       <c r="R20" t="n">
-        <v>7165463</v>
+        <v>7165724</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2691,11 +2709,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-08-09</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På sälg vid hyggeskant</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2722,10 +2735,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121589513</v>
+        <v>121589518</v>
       </c>
       <c r="B21" t="n">
-        <v>79718</v>
+        <v>74715</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2734,25 +2747,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6461</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2766,10 +2779,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>650383</v>
+        <v>650366</v>
       </c>
       <c r="R21" t="n">
-        <v>7165724</v>
+        <v>7165752</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2934,10 +2947,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121589525</v>
+        <v>121589505</v>
       </c>
       <c r="B23" t="n">
-        <v>57509</v>
+        <v>103619</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2946,25 +2959,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>222412</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2972,24 +2985,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>650311</v>
+        <v>650561</v>
       </c>
       <c r="R23" t="n">
-        <v>7165805</v>
+        <v>7165488</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3022,11 +3027,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-08-09</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Varnande läte</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3053,10 +3053,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121589532</v>
+        <v>121589516</v>
       </c>
       <c r="B24" t="n">
-        <v>74715</v>
+        <v>97065</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3065,25 +3065,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>221941</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>650059</v>
+        <v>650368</v>
       </c>
       <c r="R24" t="n">
-        <v>7165875</v>
+        <v>7165736</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>

--- a/artfynd/A 28699-2022 artfynd.xlsx
+++ b/artfynd/A 28699-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121589507</v>
+        <v>121589531</v>
       </c>
       <c r="B2" t="n">
-        <v>79719</v>
+        <v>74715</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>650583</v>
+        <v>650071</v>
       </c>
       <c r="R2" t="n">
-        <v>7165463</v>
+        <v>7165870</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,11 +755,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-08-09</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På sälg vid hyggeskant</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121589509</v>
+        <v>121589536</v>
       </c>
       <c r="B3" t="n">
-        <v>103619</v>
+        <v>97059</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,16 +797,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222412</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -830,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650424</v>
+        <v>649974</v>
       </c>
       <c r="R3" t="n">
-        <v>7165645</v>
+        <v>7165915</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -892,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121589502</v>
+        <v>121589528</v>
       </c>
       <c r="B4" t="n">
-        <v>79726</v>
+        <v>103619</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6464</v>
+        <v>222412</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -936,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>650507</v>
+        <v>650094</v>
       </c>
       <c r="R4" t="n">
-        <v>7165565</v>
+        <v>7165838</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -998,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121589535</v>
+        <v>121589527</v>
       </c>
       <c r="B5" t="n">
-        <v>82393</v>
+        <v>98126</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>221952</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1036,19 +1031,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>650021</v>
+        <v>650111</v>
       </c>
       <c r="R5" t="n">
-        <v>7165883</v>
+        <v>7165841</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1089,7 +1081,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1108,7 +1099,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121589531</v>
+        <v>121589532</v>
       </c>
       <c r="B6" t="n">
         <v>74715</v>
@@ -1152,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650071</v>
+        <v>650059</v>
       </c>
       <c r="R6" t="n">
-        <v>7165870</v>
+        <v>7165875</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1214,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121589532</v>
+        <v>121589518</v>
       </c>
       <c r="B7" t="n">
         <v>74715</v>
@@ -1258,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650059</v>
+        <v>650366</v>
       </c>
       <c r="R7" t="n">
-        <v>7165875</v>
+        <v>7165752</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1320,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121589527</v>
+        <v>121589530</v>
       </c>
       <c r="B8" t="n">
-        <v>98126</v>
+        <v>79718</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1336,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
+        <v>6461</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1364,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>650111</v>
+        <v>650084</v>
       </c>
       <c r="R8" t="n">
-        <v>7165841</v>
+        <v>7165861</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1426,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121589528</v>
+        <v>121589529</v>
       </c>
       <c r="B9" t="n">
-        <v>103619</v>
+        <v>56560</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1438,32 +1429,36 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222412</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
@@ -1473,7 +1468,7 @@
         <v>650094</v>
       </c>
       <c r="R9" t="n">
-        <v>7165838</v>
+        <v>7165843</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1506,6 +1501,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Uppflog, ca 6 yngre honor</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1532,10 +1532,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121589523</v>
+        <v>121589525</v>
       </c>
       <c r="B10" t="n">
-        <v>97059</v>
+        <v>57509</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1544,25 +1544,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1570,6 +1570,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
@@ -1579,7 +1587,7 @@
         <v>650311</v>
       </c>
       <c r="R10" t="n">
-        <v>7165804</v>
+        <v>7165805</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1612,6 +1620,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Varnande läte</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,10 +1651,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121589530</v>
+        <v>121589522</v>
       </c>
       <c r="B11" t="n">
-        <v>79718</v>
+        <v>79719</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1654,21 +1667,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6461</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1682,10 +1695,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>650084</v>
+        <v>650331</v>
       </c>
       <c r="R11" t="n">
-        <v>7165861</v>
+        <v>7165784</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1718,6 +1731,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1744,10 +1762,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121589525</v>
+        <v>121589514</v>
       </c>
       <c r="B12" t="n">
-        <v>57509</v>
+        <v>57372</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1760,21 +1778,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1782,24 +1800,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>650311</v>
+        <v>650381</v>
       </c>
       <c r="R12" t="n">
-        <v>7165805</v>
+        <v>7165754</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1836,7 +1846,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Varnande läte</t>
+          <t>Födosökshack på tallhögstubbe</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1863,10 +1873,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121589533</v>
+        <v>121589535</v>
       </c>
       <c r="B13" t="n">
-        <v>78609</v>
+        <v>82393</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1879,21 +1889,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1901,16 +1911,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>650036</v>
+        <v>650021</v>
       </c>
       <c r="R13" t="n">
-        <v>7165894</v>
+        <v>7165883</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1951,6 +1964,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1969,10 +1983,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121589536</v>
+        <v>121589533</v>
       </c>
       <c r="B14" t="n">
-        <v>97059</v>
+        <v>78609</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1981,25 +1995,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2013,10 +2027,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>649974</v>
+        <v>650036</v>
       </c>
       <c r="R14" t="n">
-        <v>7165915</v>
+        <v>7165894</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2075,7 +2089,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121589526</v>
+        <v>121589507</v>
       </c>
       <c r="B15" t="n">
         <v>79719</v>
@@ -2119,10 +2133,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>650181</v>
+        <v>650583</v>
       </c>
       <c r="R15" t="n">
-        <v>7165837</v>
+        <v>7165463</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2159,7 +2173,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På sälg vid hyggeskant</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2186,10 +2200,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121589522</v>
+        <v>121589523</v>
       </c>
       <c r="B16" t="n">
-        <v>79719</v>
+        <v>97059</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2202,21 +2216,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2230,10 +2244,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>650331</v>
+        <v>650311</v>
       </c>
       <c r="R16" t="n">
-        <v>7165784</v>
+        <v>7165804</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2266,11 +2280,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-08-09</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2297,10 +2306,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121589514</v>
+        <v>121589513</v>
       </c>
       <c r="B17" t="n">
-        <v>57372</v>
+        <v>79718</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2309,25 +2318,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6461</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2341,10 +2350,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>650381</v>
+        <v>650383</v>
       </c>
       <c r="R17" t="n">
-        <v>7165754</v>
+        <v>7165724</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2377,11 +2386,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-08-09</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Födosökshack på tallhögstubbe</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2408,10 +2412,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121589529</v>
+        <v>121589516</v>
       </c>
       <c r="B18" t="n">
-        <v>56560</v>
+        <v>97065</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2420,46 +2424,42 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102612</v>
+        <v>221941</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>650094</v>
+        <v>650368</v>
       </c>
       <c r="R18" t="n">
-        <v>7165843</v>
+        <v>7165736</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2492,11 +2492,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-08-09</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Uppflog, ca 6 yngre honor</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2629,10 +2624,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121589513</v>
+        <v>121589509</v>
       </c>
       <c r="B20" t="n">
-        <v>79718</v>
+        <v>103619</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2645,21 +2640,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6461</v>
+        <v>222412</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2673,10 +2668,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>650383</v>
+        <v>650424</v>
       </c>
       <c r="R20" t="n">
-        <v>7165724</v>
+        <v>7165645</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2735,10 +2730,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121589518</v>
+        <v>121589505</v>
       </c>
       <c r="B21" t="n">
-        <v>74715</v>
+        <v>103619</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2747,25 +2742,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>222412</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2779,10 +2774,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>650366</v>
+        <v>650561</v>
       </c>
       <c r="R21" t="n">
-        <v>7165752</v>
+        <v>7165488</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2947,10 +2942,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121589505</v>
+        <v>121589526</v>
       </c>
       <c r="B23" t="n">
-        <v>103619</v>
+        <v>79719</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2963,21 +2958,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222412</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2991,10 +2986,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>650561</v>
+        <v>650181</v>
       </c>
       <c r="R23" t="n">
-        <v>7165488</v>
+        <v>7165837</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3027,6 +3022,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3053,10 +3053,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121589516</v>
+        <v>121589502</v>
       </c>
       <c r="B24" t="n">
-        <v>97065</v>
+        <v>79726</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3069,21 +3069,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221941</v>
+        <v>6464</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>650368</v>
+        <v>650507</v>
       </c>
       <c r="R24" t="n">
-        <v>7165736</v>
+        <v>7165565</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>

--- a/artfynd/A 28699-2022 artfynd.xlsx
+++ b/artfynd/A 28699-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121589531</v>
+        <v>121589536</v>
       </c>
       <c r="B2" t="n">
-        <v>74715</v>
+        <v>97059</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>650071</v>
+        <v>649974</v>
       </c>
       <c r="R2" t="n">
-        <v>7165870</v>
+        <v>7165915</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121589536</v>
+        <v>121589531</v>
       </c>
       <c r="B3" t="n">
-        <v>97059</v>
+        <v>74715</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>649974</v>
+        <v>650071</v>
       </c>
       <c r="R3" t="n">
-        <v>7165915</v>
+        <v>7165870</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -1651,10 +1651,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121589522</v>
+        <v>121589535</v>
       </c>
       <c r="B11" t="n">
-        <v>79719</v>
+        <v>82393</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1663,25 +1663,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1689,16 +1689,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>650331</v>
+        <v>650021</v>
       </c>
       <c r="R11" t="n">
-        <v>7165784</v>
+        <v>7165883</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1733,17 +1736,13 @@
           <t>2024-08-09</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På sälg</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1873,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121589535</v>
+        <v>121589522</v>
       </c>
       <c r="B13" t="n">
-        <v>82393</v>
+        <v>79719</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1885,25 +1884,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1911,19 +1910,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>650021</v>
+        <v>650331</v>
       </c>
       <c r="R13" t="n">
-        <v>7165883</v>
+        <v>7165784</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1958,13 +1954,17 @@
           <t>2024-08-09</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2200,10 +2200,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121589523</v>
+        <v>121589513</v>
       </c>
       <c r="B16" t="n">
-        <v>97059</v>
+        <v>79718</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2216,21 +2216,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>6461</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2244,10 +2244,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>650311</v>
+        <v>650383</v>
       </c>
       <c r="R16" t="n">
-        <v>7165804</v>
+        <v>7165724</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2306,10 +2306,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121589513</v>
+        <v>121589523</v>
       </c>
       <c r="B17" t="n">
-        <v>79718</v>
+        <v>97059</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2322,21 +2322,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6461</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2350,10 +2350,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>650383</v>
+        <v>650311</v>
       </c>
       <c r="R17" t="n">
-        <v>7165724</v>
+        <v>7165804</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>

--- a/artfynd/A 28699-2022 artfynd.xlsx
+++ b/artfynd/A 28699-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121589536</v>
+        <v>121589522</v>
       </c>
       <c r="B2" t="n">
-        <v>97059</v>
+        <v>79726</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>649974</v>
+        <v>650331</v>
       </c>
       <c r="R2" t="n">
-        <v>7165915</v>
+        <v>7165784</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,6 +755,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121589531</v>
+        <v>121589529</v>
       </c>
       <c r="B3" t="n">
-        <v>74715</v>
+        <v>56561</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,38 +802,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650071</v>
+        <v>650094</v>
       </c>
       <c r="R3" t="n">
-        <v>7165870</v>
+        <v>7165843</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -861,6 +870,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Uppflog, ca 6 yngre honor</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121589528</v>
+        <v>121589536</v>
       </c>
       <c r="B4" t="n">
-        <v>103619</v>
+        <v>97067</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,16 +917,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222412</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -931,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>650094</v>
+        <v>649974</v>
       </c>
       <c r="R4" t="n">
-        <v>7165838</v>
+        <v>7165915</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -993,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121589527</v>
+        <v>121589513</v>
       </c>
       <c r="B5" t="n">
-        <v>98126</v>
+        <v>79725</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1023,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221952</v>
+        <v>6461</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>650111</v>
+        <v>650383</v>
       </c>
       <c r="R5" t="n">
-        <v>7165841</v>
+        <v>7165724</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1099,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121589532</v>
+        <v>121589533</v>
       </c>
       <c r="B6" t="n">
-        <v>74715</v>
+        <v>78616</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1129,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1143,10 +1157,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650059</v>
+        <v>650036</v>
       </c>
       <c r="R6" t="n">
-        <v>7165875</v>
+        <v>7165894</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1205,10 +1219,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121589518</v>
+        <v>121589509</v>
       </c>
       <c r="B7" t="n">
-        <v>74715</v>
+        <v>103627</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1231,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>222412</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1249,10 +1263,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650366</v>
+        <v>650424</v>
       </c>
       <c r="R7" t="n">
-        <v>7165752</v>
+        <v>7165645</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1311,10 +1325,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121589530</v>
+        <v>121589525</v>
       </c>
       <c r="B8" t="n">
-        <v>79718</v>
+        <v>57510</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,25 +1337,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6461</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1349,16 +1363,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>650084</v>
+        <v>650311</v>
       </c>
       <c r="R8" t="n">
-        <v>7165861</v>
+        <v>7165805</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1391,6 +1413,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Varnande läte</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1417,10 +1444,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121589529</v>
+        <v>121589516</v>
       </c>
       <c r="B9" t="n">
-        <v>56560</v>
+        <v>97073</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,46 +1456,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>221941</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>650094</v>
+        <v>650368</v>
       </c>
       <c r="R9" t="n">
-        <v>7165843</v>
+        <v>7165736</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1501,11 +1524,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-08-09</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Uppflog, ca 6 yngre honor</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1532,10 +1550,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121589525</v>
+        <v>121589523</v>
       </c>
       <c r="B10" t="n">
-        <v>57509</v>
+        <v>97067</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1544,25 +1562,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1570,14 +1588,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
@@ -1587,7 +1597,7 @@
         <v>650311</v>
       </c>
       <c r="R10" t="n">
-        <v>7165805</v>
+        <v>7165804</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1620,11 +1630,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-08-09</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Varnande läte</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1651,10 +1656,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121589535</v>
+        <v>121589532</v>
       </c>
       <c r="B11" t="n">
-        <v>82393</v>
+        <v>74722</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1667,21 +1672,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1689,19 +1694,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>650021</v>
+        <v>650059</v>
       </c>
       <c r="R11" t="n">
-        <v>7165883</v>
+        <v>7165875</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1742,7 +1744,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1761,10 +1762,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121589514</v>
+        <v>121589531</v>
       </c>
       <c r="B12" t="n">
-        <v>57372</v>
+        <v>74722</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1777,21 +1778,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1805,10 +1806,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>650381</v>
+        <v>650071</v>
       </c>
       <c r="R12" t="n">
-        <v>7165754</v>
+        <v>7165870</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1841,11 +1842,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-08-09</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Födosökshack på tallhögstubbe</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1872,10 +1868,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121589522</v>
+        <v>121589507</v>
       </c>
       <c r="B13" t="n">
-        <v>79719</v>
+        <v>79726</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1916,10 +1912,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>650331</v>
+        <v>650583</v>
       </c>
       <c r="R13" t="n">
-        <v>7165784</v>
+        <v>7165463</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1956,7 +1952,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På sälg vid hyggeskant</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1983,10 +1979,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121589533</v>
+        <v>121589526</v>
       </c>
       <c r="B14" t="n">
-        <v>78609</v>
+        <v>79726</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1995,25 +1991,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2027,10 +2023,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>650036</v>
+        <v>650181</v>
       </c>
       <c r="R14" t="n">
-        <v>7165894</v>
+        <v>7165837</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2063,6 +2059,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2089,10 +2090,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121589507</v>
+        <v>121589501</v>
       </c>
       <c r="B15" t="n">
-        <v>79719</v>
+        <v>79726</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2133,10 +2134,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>650583</v>
+        <v>650510</v>
       </c>
       <c r="R15" t="n">
-        <v>7165463</v>
+        <v>7165564</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2169,11 +2170,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-08-09</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På sälg vid hyggeskant</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2200,10 +2196,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121589513</v>
+        <v>121589538</v>
       </c>
       <c r="B16" t="n">
-        <v>79718</v>
+        <v>103627</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2216,21 +2212,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6461</v>
+        <v>222412</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2244,10 +2240,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>650383</v>
+        <v>649959</v>
       </c>
       <c r="R16" t="n">
-        <v>7165724</v>
+        <v>7165924</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2306,10 +2302,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121589523</v>
+        <v>121589514</v>
       </c>
       <c r="B17" t="n">
-        <v>97059</v>
+        <v>57373</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2318,25 +2314,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2350,10 +2346,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>650311</v>
+        <v>650381</v>
       </c>
       <c r="R17" t="n">
-        <v>7165804</v>
+        <v>7165754</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2386,6 +2382,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Födosökshack på tallhögstubbe</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2412,10 +2413,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121589516</v>
+        <v>121589528</v>
       </c>
       <c r="B18" t="n">
-        <v>97065</v>
+        <v>103627</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2428,16 +2429,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221941</v>
+        <v>222412</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2456,10 +2457,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>650368</v>
+        <v>650094</v>
       </c>
       <c r="R18" t="n">
-        <v>7165736</v>
+        <v>7165838</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2518,10 +2519,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121589538</v>
+        <v>121589530</v>
       </c>
       <c r="B19" t="n">
-        <v>103619</v>
+        <v>79725</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2534,21 +2535,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222412</v>
+        <v>6461</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2562,10 +2563,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>649959</v>
+        <v>650084</v>
       </c>
       <c r="R19" t="n">
-        <v>7165924</v>
+        <v>7165861</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2624,10 +2625,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121589509</v>
+        <v>121589527</v>
       </c>
       <c r="B20" t="n">
-        <v>103619</v>
+        <v>98134</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2640,21 +2641,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222412</v>
+        <v>221952</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2668,10 +2669,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>650424</v>
+        <v>650111</v>
       </c>
       <c r="R20" t="n">
-        <v>7165645</v>
+        <v>7165841</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2730,10 +2731,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121589505</v>
+        <v>121589502</v>
       </c>
       <c r="B21" t="n">
-        <v>103619</v>
+        <v>79733</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2746,21 +2747,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222412</v>
+        <v>6464</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2774,10 +2775,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>650561</v>
+        <v>650507</v>
       </c>
       <c r="R21" t="n">
-        <v>7165488</v>
+        <v>7165565</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2836,10 +2837,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121589501</v>
+        <v>121589535</v>
       </c>
       <c r="B22" t="n">
-        <v>79719</v>
+        <v>82400</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2848,25 +2849,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2874,16 +2875,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>650510</v>
+        <v>650021</v>
       </c>
       <c r="R22" t="n">
-        <v>7165564</v>
+        <v>7165883</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2924,6 +2928,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2942,10 +2947,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121589526</v>
+        <v>121589505</v>
       </c>
       <c r="B23" t="n">
-        <v>79719</v>
+        <v>103627</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2958,21 +2963,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>222412</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2986,10 +2991,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>650181</v>
+        <v>650561</v>
       </c>
       <c r="R23" t="n">
-        <v>7165837</v>
+        <v>7165488</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3022,11 +3027,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-08-09</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3053,10 +3053,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121589502</v>
+        <v>121589518</v>
       </c>
       <c r="B24" t="n">
-        <v>79726</v>
+        <v>74722</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3065,25 +3065,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6464</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>650507</v>
+        <v>650366</v>
       </c>
       <c r="R24" t="n">
-        <v>7165565</v>
+        <v>7165752</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>

--- a/artfynd/A 28699-2022 artfynd.xlsx
+++ b/artfynd/A 28699-2022 artfynd.xlsx
@@ -1113,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121589533</v>
+        <v>121589509</v>
       </c>
       <c r="B6" t="n">
-        <v>78616</v>
+        <v>103627</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1125,25 +1125,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>222412</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1157,10 +1157,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650036</v>
+        <v>650424</v>
       </c>
       <c r="R6" t="n">
-        <v>7165894</v>
+        <v>7165645</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1219,10 +1219,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121589509</v>
+        <v>121589533</v>
       </c>
       <c r="B7" t="n">
-        <v>103627</v>
+        <v>78616</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1231,25 +1231,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222412</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1263,10 +1263,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650424</v>
+        <v>650036</v>
       </c>
       <c r="R7" t="n">
-        <v>7165645</v>
+        <v>7165894</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -2625,10 +2625,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121589527</v>
+        <v>121589502</v>
       </c>
       <c r="B20" t="n">
-        <v>98134</v>
+        <v>79733</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2641,21 +2641,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221952</v>
+        <v>6464</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2669,10 +2669,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>650111</v>
+        <v>650507</v>
       </c>
       <c r="R20" t="n">
-        <v>7165841</v>
+        <v>7165565</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2731,10 +2731,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121589502</v>
+        <v>121589527</v>
       </c>
       <c r="B21" t="n">
-        <v>79733</v>
+        <v>98134</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2747,21 +2747,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6464</v>
+        <v>221952</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2775,10 +2775,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>650507</v>
+        <v>650111</v>
       </c>
       <c r="R21" t="n">
-        <v>7165565</v>
+        <v>7165841</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>

--- a/artfynd/A 28699-2022 artfynd.xlsx
+++ b/artfynd/A 28699-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121589532</v>
+        <v>121589533</v>
       </c>
       <c r="B2" t="n">
-        <v>74722</v>
+        <v>78616</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>650059</v>
+        <v>650036</v>
       </c>
       <c r="R2" t="n">
-        <v>7165875</v>
+        <v>7165894</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121589527</v>
+        <v>121589525</v>
       </c>
       <c r="B3" t="n">
-        <v>98134</v>
+        <v>57510</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -819,16 +819,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650111</v>
+        <v>650311</v>
       </c>
       <c r="R3" t="n">
-        <v>7165841</v>
+        <v>7165805</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -861,6 +869,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Varnande läte</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121589522</v>
+        <v>121589536</v>
       </c>
       <c r="B4" t="n">
-        <v>79726</v>
+        <v>97067</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +916,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>650331</v>
+        <v>649974</v>
       </c>
       <c r="R4" t="n">
-        <v>7165784</v>
+        <v>7165915</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -967,11 +980,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-08-09</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121589525</v>
+        <v>121589507</v>
       </c>
       <c r="B5" t="n">
-        <v>57510</v>
+        <v>79726</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,25 +1018,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1036,24 +1044,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>650311</v>
+        <v>650583</v>
       </c>
       <c r="R5" t="n">
-        <v>7165805</v>
+        <v>7165463</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Varnande läte</t>
+          <t>På sälg vid hyggeskant</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,10 +1117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121589538</v>
+        <v>121589501</v>
       </c>
       <c r="B6" t="n">
-        <v>103627</v>
+        <v>79726</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1133,21 +1133,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222412</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>649959</v>
+        <v>650510</v>
       </c>
       <c r="R6" t="n">
-        <v>7165924</v>
+        <v>7165564</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1338,10 +1338,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121589507</v>
+        <v>121589532</v>
       </c>
       <c r="B8" t="n">
-        <v>79726</v>
+        <v>74722</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1350,25 +1350,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>650583</v>
+        <v>650059</v>
       </c>
       <c r="R8" t="n">
-        <v>7165463</v>
+        <v>7165875</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1418,11 +1418,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-08-09</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På sälg vid hyggeskant</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1449,10 +1444,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121589526</v>
+        <v>121589527</v>
       </c>
       <c r="B9" t="n">
-        <v>79726</v>
+        <v>98134</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1465,21 +1460,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1493,10 +1488,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>650181</v>
+        <v>650111</v>
       </c>
       <c r="R9" t="n">
-        <v>7165837</v>
+        <v>7165841</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1529,11 +1524,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-08-09</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1560,10 +1550,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121589502</v>
+        <v>121589528</v>
       </c>
       <c r="B10" t="n">
-        <v>79733</v>
+        <v>103627</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1576,21 +1566,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6464</v>
+        <v>222412</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1604,10 +1594,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>650507</v>
+        <v>650094</v>
       </c>
       <c r="R10" t="n">
-        <v>7165565</v>
+        <v>7165838</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1666,10 +1656,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121589513</v>
+        <v>121589516</v>
       </c>
       <c r="B11" t="n">
-        <v>79725</v>
+        <v>97073</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1682,21 +1672,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6461</v>
+        <v>221941</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1710,10 +1700,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>650383</v>
+        <v>650368</v>
       </c>
       <c r="R11" t="n">
-        <v>7165724</v>
+        <v>7165736</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1772,10 +1762,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121589518</v>
+        <v>121589509</v>
       </c>
       <c r="B12" t="n">
-        <v>74722</v>
+        <v>103627</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1784,25 +1774,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>222412</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1816,10 +1806,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>650366</v>
+        <v>650424</v>
       </c>
       <c r="R12" t="n">
-        <v>7165752</v>
+        <v>7165645</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1878,10 +1868,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121589505</v>
+        <v>121589513</v>
       </c>
       <c r="B13" t="n">
-        <v>103627</v>
+        <v>79725</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1894,21 +1884,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222412</v>
+        <v>6461</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1922,10 +1912,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>650561</v>
+        <v>650383</v>
       </c>
       <c r="R13" t="n">
-        <v>7165488</v>
+        <v>7165724</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1984,10 +1974,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121589528</v>
+        <v>121589526</v>
       </c>
       <c r="B14" t="n">
-        <v>103627</v>
+        <v>79726</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2000,21 +1990,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222412</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2028,10 +2018,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>650094</v>
+        <v>650181</v>
       </c>
       <c r="R14" t="n">
-        <v>7165838</v>
+        <v>7165837</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2064,6 +2054,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2090,10 +2085,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121589501</v>
+        <v>121589538</v>
       </c>
       <c r="B15" t="n">
-        <v>79726</v>
+        <v>103627</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2106,21 +2101,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>222412</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2134,10 +2129,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>650510</v>
+        <v>649959</v>
       </c>
       <c r="R15" t="n">
-        <v>7165564</v>
+        <v>7165924</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2196,10 +2191,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121589509</v>
+        <v>121589535</v>
       </c>
       <c r="B16" t="n">
-        <v>103627</v>
+        <v>82400</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2208,25 +2203,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222412</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2234,16 +2229,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>650424</v>
+        <v>650021</v>
       </c>
       <c r="R16" t="n">
-        <v>7165645</v>
+        <v>7165883</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2284,6 +2282,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2302,10 +2301,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121589514</v>
+        <v>121589518</v>
       </c>
       <c r="B17" t="n">
-        <v>57373</v>
+        <v>74722</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2318,21 +2317,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2346,10 +2345,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>650381</v>
+        <v>650366</v>
       </c>
       <c r="R17" t="n">
-        <v>7165754</v>
+        <v>7165752</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2382,11 +2381,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-08-09</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Födosökshack på tallhögstubbe</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2413,7 +2407,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121589536</v>
+        <v>121589523</v>
       </c>
       <c r="B18" t="n">
         <v>97067</v>
@@ -2457,10 +2451,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>649974</v>
+        <v>650311</v>
       </c>
       <c r="R18" t="n">
-        <v>7165915</v>
+        <v>7165804</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2519,10 +2513,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121589523</v>
+        <v>121589530</v>
       </c>
       <c r="B19" t="n">
-        <v>97067</v>
+        <v>79725</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2535,21 +2529,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>6461</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2563,10 +2557,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>650311</v>
+        <v>650084</v>
       </c>
       <c r="R19" t="n">
-        <v>7165804</v>
+        <v>7165861</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2625,10 +2619,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121589533</v>
+        <v>121589531</v>
       </c>
       <c r="B20" t="n">
-        <v>78616</v>
+        <v>74722</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2641,21 +2635,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2669,10 +2663,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>650036</v>
+        <v>650071</v>
       </c>
       <c r="R20" t="n">
-        <v>7165894</v>
+        <v>7165870</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2731,10 +2725,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121589531</v>
+        <v>121589502</v>
       </c>
       <c r="B21" t="n">
-        <v>74722</v>
+        <v>79733</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2743,25 +2737,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>6464</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2775,10 +2769,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>650071</v>
+        <v>650507</v>
       </c>
       <c r="R21" t="n">
-        <v>7165870</v>
+        <v>7165565</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2837,10 +2831,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121589535</v>
+        <v>121589514</v>
       </c>
       <c r="B22" t="n">
-        <v>82400</v>
+        <v>57373</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2853,21 +2847,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2875,19 +2869,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>650021</v>
+        <v>650381</v>
       </c>
       <c r="R22" t="n">
-        <v>7165883</v>
+        <v>7165754</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2922,13 +2913,17 @@
           <t>2024-08-09</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Födosökshack på tallhögstubbe</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2947,10 +2942,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121589530</v>
+        <v>121589505</v>
       </c>
       <c r="B23" t="n">
-        <v>79725</v>
+        <v>103627</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2963,21 +2958,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6461</v>
+        <v>222412</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2991,10 +2986,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>650084</v>
+        <v>650561</v>
       </c>
       <c r="R23" t="n">
-        <v>7165861</v>
+        <v>7165488</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3053,10 +3048,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121589516</v>
+        <v>121589522</v>
       </c>
       <c r="B24" t="n">
-        <v>97073</v>
+        <v>79726</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3069,21 +3064,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221941</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3097,10 +3092,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>650368</v>
+        <v>650331</v>
       </c>
       <c r="R24" t="n">
-        <v>7165736</v>
+        <v>7165784</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3133,6 +3128,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 28699-2022 artfynd.xlsx
+++ b/artfynd/A 28699-2022 artfynd.xlsx
@@ -1117,10 +1117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121589501</v>
+        <v>121589529</v>
       </c>
       <c r="B6" t="n">
-        <v>79726</v>
+        <v>56561</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,42 +1129,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>102612</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650510</v>
+        <v>650094</v>
       </c>
       <c r="R6" t="n">
-        <v>7165564</v>
+        <v>7165843</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1197,6 +1201,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Uppflog, ca 6 yngre honor</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,10 +1232,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121589529</v>
+        <v>121589501</v>
       </c>
       <c r="B7" t="n">
-        <v>56561</v>
+        <v>79726</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1235,46 +1244,42 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102612</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650094</v>
+        <v>650510</v>
       </c>
       <c r="R7" t="n">
-        <v>7165843</v>
+        <v>7165564</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1307,11 +1312,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-08-09</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Uppflog, ca 6 yngre honor</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -2191,10 +2191,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121589535</v>
+        <v>121589523</v>
       </c>
       <c r="B16" t="n">
-        <v>82400</v>
+        <v>97067</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2203,25 +2203,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2229,19 +2229,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>650021</v>
+        <v>650311</v>
       </c>
       <c r="R16" t="n">
-        <v>7165883</v>
+        <v>7165804</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2282,7 +2279,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2301,10 +2297,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121589518</v>
+        <v>121589535</v>
       </c>
       <c r="B17" t="n">
-        <v>74722</v>
+        <v>82400</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2317,21 +2313,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2339,16 +2335,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>650366</v>
+        <v>650021</v>
       </c>
       <c r="R17" t="n">
-        <v>7165752</v>
+        <v>7165883</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2389,6 +2388,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2407,10 +2407,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121589523</v>
+        <v>121589518</v>
       </c>
       <c r="B18" t="n">
-        <v>97067</v>
+        <v>74722</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2419,25 +2419,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2451,10 +2451,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>650311</v>
+        <v>650366</v>
       </c>
       <c r="R18" t="n">
-        <v>7165804</v>
+        <v>7165752</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2725,10 +2725,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121589502</v>
+        <v>121589522</v>
       </c>
       <c r="B21" t="n">
-        <v>79733</v>
+        <v>79726</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2741,21 +2741,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2769,10 +2769,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>650507</v>
+        <v>650331</v>
       </c>
       <c r="R21" t="n">
-        <v>7165565</v>
+        <v>7165784</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2805,6 +2805,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2831,10 +2836,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121589514</v>
+        <v>121589502</v>
       </c>
       <c r="B22" t="n">
-        <v>57373</v>
+        <v>79733</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2843,25 +2848,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6464</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2875,10 +2880,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>650381</v>
+        <v>650507</v>
       </c>
       <c r="R22" t="n">
-        <v>7165754</v>
+        <v>7165565</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2911,11 +2916,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-08-09</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Födosökshack på tallhögstubbe</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2942,10 +2942,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121589505</v>
+        <v>121589514</v>
       </c>
       <c r="B23" t="n">
-        <v>103627</v>
+        <v>57373</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2954,25 +2954,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222412</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2986,10 +2986,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>650561</v>
+        <v>650381</v>
       </c>
       <c r="R23" t="n">
-        <v>7165488</v>
+        <v>7165754</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3022,6 +3022,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Födosökshack på tallhögstubbe</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3048,10 +3053,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121589522</v>
+        <v>121589505</v>
       </c>
       <c r="B24" t="n">
-        <v>79726</v>
+        <v>103627</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3064,21 +3069,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>222412</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3092,10 +3097,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>650331</v>
+        <v>650561</v>
       </c>
       <c r="R24" t="n">
-        <v>7165784</v>
+        <v>7165488</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3128,11 +3133,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-08-09</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 28699-2022 artfynd.xlsx
+++ b/artfynd/A 28699-2022 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121589525</v>
+        <v>121589516</v>
       </c>
       <c r="B3" t="n">
-        <v>57510</v>
+        <v>97073</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -819,24 +819,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650311</v>
+        <v>650368</v>
       </c>
       <c r="R3" t="n">
-        <v>7165805</v>
+        <v>7165736</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,11 +861,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-08-09</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Varnande läte</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121589536</v>
+        <v>121589501</v>
       </c>
       <c r="B4" t="n">
-        <v>97067</v>
+        <v>79726</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -944,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>649974</v>
+        <v>650510</v>
       </c>
       <c r="R4" t="n">
-        <v>7165915</v>
+        <v>7165564</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1006,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121589507</v>
+        <v>121589530</v>
       </c>
       <c r="B5" t="n">
-        <v>79726</v>
+        <v>79725</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>6461</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1050,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>650583</v>
+        <v>650084</v>
       </c>
       <c r="R5" t="n">
-        <v>7165463</v>
+        <v>7165861</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1086,11 +1073,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-08-09</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På sälg vid hyggeskant</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121589529</v>
+        <v>121589502</v>
       </c>
       <c r="B6" t="n">
-        <v>56561</v>
+        <v>79733</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,46 +1111,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>6464</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650094</v>
+        <v>650507</v>
       </c>
       <c r="R6" t="n">
-        <v>7165843</v>
+        <v>7165565</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1201,11 +1179,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-08-09</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Uppflog, ca 6 yngre honor</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121589501</v>
+        <v>121589536</v>
       </c>
       <c r="B7" t="n">
-        <v>79726</v>
+        <v>97067</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1248,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1276,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650510</v>
+        <v>649974</v>
       </c>
       <c r="R7" t="n">
-        <v>7165564</v>
+        <v>7165915</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1338,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121589532</v>
+        <v>121589523</v>
       </c>
       <c r="B8" t="n">
-        <v>74722</v>
+        <v>97067</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1350,25 +1323,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1382,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>650059</v>
+        <v>650311</v>
       </c>
       <c r="R8" t="n">
-        <v>7165875</v>
+        <v>7165804</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1444,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121589527</v>
+        <v>121589528</v>
       </c>
       <c r="B9" t="n">
-        <v>98134</v>
+        <v>103627</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1460,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>222412</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1488,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>650111</v>
+        <v>650094</v>
       </c>
       <c r="R9" t="n">
-        <v>7165841</v>
+        <v>7165838</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1550,7 +1523,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121589528</v>
+        <v>121589505</v>
       </c>
       <c r="B10" t="n">
         <v>103627</v>
@@ -1594,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>650094</v>
+        <v>650561</v>
       </c>
       <c r="R10" t="n">
-        <v>7165838</v>
+        <v>7165488</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1656,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121589516</v>
+        <v>121589513</v>
       </c>
       <c r="B11" t="n">
-        <v>97073</v>
+        <v>79725</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1672,21 +1645,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221941</v>
+        <v>6461</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1700,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>650368</v>
+        <v>650383</v>
       </c>
       <c r="R11" t="n">
-        <v>7165736</v>
+        <v>7165724</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1762,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121589509</v>
+        <v>121589507</v>
       </c>
       <c r="B12" t="n">
-        <v>103627</v>
+        <v>79726</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1778,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222412</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1806,10 +1779,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>650424</v>
+        <v>650583</v>
       </c>
       <c r="R12" t="n">
-        <v>7165645</v>
+        <v>7165463</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1842,6 +1815,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På sälg vid hyggeskant</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1868,10 +1846,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121589513</v>
+        <v>121589527</v>
       </c>
       <c r="B13" t="n">
-        <v>79725</v>
+        <v>98134</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1884,21 +1862,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6461</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1912,10 +1890,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>650383</v>
+        <v>650111</v>
       </c>
       <c r="R13" t="n">
-        <v>7165724</v>
+        <v>7165841</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1974,10 +1952,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121589526</v>
+        <v>121589529</v>
       </c>
       <c r="B14" t="n">
-        <v>79726</v>
+        <v>56561</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1986,42 +1964,46 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>102612</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>650181</v>
+        <v>650094</v>
       </c>
       <c r="R14" t="n">
-        <v>7165837</v>
+        <v>7165843</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2058,7 +2040,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>Uppflog, ca 6 yngre honor</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2085,7 +2067,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121589538</v>
+        <v>121589509</v>
       </c>
       <c r="B15" t="n">
         <v>103627</v>
@@ -2129,10 +2111,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>649959</v>
+        <v>650424</v>
       </c>
       <c r="R15" t="n">
-        <v>7165924</v>
+        <v>7165645</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2191,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121589523</v>
+        <v>121589522</v>
       </c>
       <c r="B16" t="n">
-        <v>97067</v>
+        <v>79726</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2207,21 +2189,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2235,10 +2217,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>650311</v>
+        <v>650331</v>
       </c>
       <c r="R16" t="n">
-        <v>7165804</v>
+        <v>7165784</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2271,6 +2253,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2297,10 +2284,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121589535</v>
+        <v>121589531</v>
       </c>
       <c r="B17" t="n">
-        <v>82400</v>
+        <v>74722</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2313,21 +2300,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2335,19 +2322,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>650021</v>
+        <v>650071</v>
       </c>
       <c r="R17" t="n">
-        <v>7165883</v>
+        <v>7165870</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2388,7 +2372,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2407,10 +2390,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121589518</v>
+        <v>121589514</v>
       </c>
       <c r="B18" t="n">
-        <v>74722</v>
+        <v>57373</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2423,21 +2406,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2451,10 +2434,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>650366</v>
+        <v>650381</v>
       </c>
       <c r="R18" t="n">
-        <v>7165752</v>
+        <v>7165754</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2487,6 +2470,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Födosökshack på tallhögstubbe</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2513,10 +2501,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121589530</v>
+        <v>121589525</v>
       </c>
       <c r="B19" t="n">
-        <v>79725</v>
+        <v>57510</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2525,25 +2513,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6461</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2551,16 +2539,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>650084</v>
+        <v>650311</v>
       </c>
       <c r="R19" t="n">
-        <v>7165861</v>
+        <v>7165805</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2593,6 +2589,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Varnande läte</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2619,10 +2620,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121589531</v>
+        <v>121589526</v>
       </c>
       <c r="B20" t="n">
-        <v>74722</v>
+        <v>79726</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2631,25 +2632,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2663,10 +2664,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>650071</v>
+        <v>650181</v>
       </c>
       <c r="R20" t="n">
-        <v>7165870</v>
+        <v>7165837</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2699,6 +2700,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2725,10 +2731,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121589522</v>
+        <v>121589532</v>
       </c>
       <c r="B21" t="n">
-        <v>79726</v>
+        <v>74722</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2737,25 +2743,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2769,10 +2775,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>650331</v>
+        <v>650059</v>
       </c>
       <c r="R21" t="n">
-        <v>7165784</v>
+        <v>7165875</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2805,11 +2811,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-08-09</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2836,10 +2837,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121589502</v>
+        <v>121589518</v>
       </c>
       <c r="B22" t="n">
-        <v>79733</v>
+        <v>74722</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2848,25 +2849,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6464</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2880,10 +2881,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>650507</v>
+        <v>650366</v>
       </c>
       <c r="R22" t="n">
-        <v>7165565</v>
+        <v>7165752</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2942,10 +2943,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121589514</v>
+        <v>121589535</v>
       </c>
       <c r="B23" t="n">
-        <v>57373</v>
+        <v>82400</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2958,21 +2959,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2980,16 +2981,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>650381</v>
+        <v>650021</v>
       </c>
       <c r="R23" t="n">
-        <v>7165754</v>
+        <v>7165883</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3024,17 +3028,13 @@
           <t>2024-08-09</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Födosökshack på tallhögstubbe</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3053,7 +3053,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121589505</v>
+        <v>121589538</v>
       </c>
       <c r="B24" t="n">
         <v>103627</v>
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>650561</v>
+        <v>649959</v>
       </c>
       <c r="R24" t="n">
-        <v>7165488</v>
+        <v>7165924</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
